--- a/results_clean.xlsx
+++ b/results_clean.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdnl\Desktop\phd_local\pub_webmaps_codecomplexity_performance\webmaplibs_performance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10EB3B1-B6BB-4EFD-B5AB-9171D437BC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E5A093-49A9-4D67-9A4A-13A5D7D926B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1305" windowWidth="26985" windowHeight="13035" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Points" sheetId="1" r:id="rId1"/>
     <sheet name="Points_3070PC" sheetId="6" r:id="rId2"/>
     <sheet name="Lines_3070PC" sheetId="8" r:id="rId3"/>
     <sheet name="Polygons_3070PC" sheetId="9" r:id="rId4"/>
-    <sheet name="STDDEV AVERAGES" sheetId="11" r:id="rId5"/>
-    <sheet name="DatasetSizes" sheetId="10" r:id="rId6"/>
+    <sheet name="Combined_3070PC" sheetId="12" r:id="rId5"/>
+    <sheet name="STDDEV AVERAGES" sheetId="11" r:id="rId6"/>
+    <sheet name="DatasetSizes" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="68">
   <si>
     <t>Run #</t>
   </si>
@@ -202,13 +203,49 @@
     <t>MapLibre GL JS</t>
   </si>
   <si>
-    <t>avg</t>
-  </si>
-  <si>
     <t>Rendering speed consistency of libraries (ms)</t>
   </si>
   <si>
     <t>3070 / R5 3600</t>
+  </si>
+  <si>
+    <t>COMBINED (3 LAYERS of all geom-types)</t>
+  </si>
+  <si>
+    <t>Combined</t>
+  </si>
+  <si>
+    <t>500*3</t>
+  </si>
+  <si>
+    <t>1000*3</t>
+  </si>
+  <si>
+    <t>5000*3</t>
+  </si>
+  <si>
+    <t>10000*3</t>
+  </si>
+  <si>
+    <t>50000*3</t>
+  </si>
+  <si>
+    <t>500000*3</t>
+  </si>
+  <si>
+    <t>100000*3</t>
+  </si>
+  <si>
+    <t>50*3</t>
+  </si>
+  <si>
+    <t>100*3</t>
+  </si>
+  <si>
+    <t>Feature count (N features * 3 types)</t>
+  </si>
+  <si>
+    <t>Std.dev avg:</t>
   </si>
 </sst>
 </file>
@@ -464,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -497,11 +534,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1376,6 +1419,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1383,7 +1427,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2277,6 +2320,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2284,7 +2328,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3088,6 +3131,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3095,7 +3139,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3916,6 +3959,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3923,7 +3967,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3954,6 +3997,2529 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="sk-SK" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Full chart: 50*3 - 50000*3 combined features</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Leaflet 1.9.4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$15:$J$15</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$15:$H$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>379.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>730.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3540.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9E9-4CE7-A8DA-B584B37B9DCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MBoxGLJS 3.7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$33:$J$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$33:$H$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>178.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>181.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>211.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>255.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>472.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>641.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2192.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C9E9-4CE7-A8DA-B584B37B9DCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MLibGLJS 4.7.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$51:$J$51</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$51:$H$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>350.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>351.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>351.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>354.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>706.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1196.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4910.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C9E9-4CE7-A8DA-B584B37B9DCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OpenLayers 10.2.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$69:$J$69</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$69:$H$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>283.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>495.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2112.8000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C9E9-4CE7-A8DA-B584B37B9DCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="444999919"/>
+        <c:axId val="445001359"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="444999919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="sk-SK" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Combined dataset</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="sk-SK" sz="1200" b="1" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> (f</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="sk-SK" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>eature count)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="445001359"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="445001359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="sk-SK" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Time (ms)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.6405667412378821E-2"/>
+              <c:y val="0.42257846817365263"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="444999919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="sk-SK"/>
+              <a:t>Excerpt for 50*3 - 10000*3 combined features</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Leaflet 1.9.4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$15:$J$15</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$15:$G$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>379.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>730.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-902B-4AD5-8D30-4037C3CB0F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MBoxGLJS 3.7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$33:$J$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$33:$G$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>178.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>181.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>211.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>255.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>472.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>641.70000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-902B-4AD5-8D30-4037C3CB0F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MLibGLJS 4.7.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$51:$J$51</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$51:$G$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>350.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>351.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>351.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>354.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>706.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1196.5999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-902B-4AD5-8D30-4037C3CB0F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OpenLayers 10.2.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$69:$J$69</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$69:$G$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>283.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>495.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-902B-4AD5-8D30-4037C3CB0F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="444999919"/>
+        <c:axId val="445001359"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="444999919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="sk-SK"/>
+                  <a:t>Feature count</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="445001359"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="445001359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="sk-SK"/>
+                  <a:t>Time (ms)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.6405667412378821E-2"/>
+              <c:y val="0.42257846817365263"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="444999919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Leaflet 1.9.4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$15:$J$15</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$15:$H$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>379.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>730.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3540.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4890-4C39-8401-7A2D1290F48E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MBoxGLJS 3.7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$33:$J$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$33:$H$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>178.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>181.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>211.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>255.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>472.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>641.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2192.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4890-4C39-8401-7A2D1290F48E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MLibGLJS 4.7.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$51:$J$51</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$51:$H$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>350.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>351.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>351.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>354.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>706.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1196.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4910.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4890-4C39-8401-7A2D1290F48E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_3070PC!$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OpenLayers 10.2.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$4:$J$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$4:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50*3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100*3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500*3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000*3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000*3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000*3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50000*3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Combined_3070PC!$B$69:$J$69</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Combined_3070PC!$B$69:$H$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>283.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>495.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2112.8000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4890-4C39-8401-7A2D1290F48E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="444999919"/>
+        <c:axId val="445001359"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="444999919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="sk-SK" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Combined dataset (feature count)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="445001359"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="445001359"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="sk-SK" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Time (ms)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.6405667412378821E-2"/>
+              <c:y val="0.42257846817365263"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="444999919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4352,6 +6918,136 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-0AEF-48FB-A856-8B465FFA5DBE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'STDDEV AVERAGES'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Combined</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inBase"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'STDDEV AVERAGES'!$B$2:$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Leaflet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Mapbox GL JS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>MapLibre GL JS</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OpenLayers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'STDDEV AVERAGES'!$B$6:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.6465432904702295</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.937662698894353</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.674740984882316</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.6959145865774667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8B90-462D-881A-18252E18870E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4520,6 +7216,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4527,7 +7224,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5331,6 +8027,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5338,7 +8035,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6164,6 +8860,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6171,7 +8868,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7055,6 +9751,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7062,7 +9759,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7866,6 +10562,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7873,7 +10570,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8685,6 +11381,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8692,7 +11389,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9589,6 +12285,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9596,7 +12293,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10400,6 +13096,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10407,7 +13104,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11252,6 +13948,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11259,7 +13956,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11450,6 +14146,126 @@
 </file>
 
 <file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent4"/>
@@ -14386,6 +17202,1554 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -18709,16 +23073,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:colOff>495300</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>147639</xdr:rowOff>
+      <xdr:rowOff>109539</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18990,6 +23354,125 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6654AE93-F219-4893-9694-06C84DE7792F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A3B1C80-8C33-4269-A651-08C67BCBF335}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90E1DDFB-E674-4743-A6A5-A8FFD8507692}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -18998,7 +23481,7 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -19297,34 +23780,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="29.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33"/>
-      <c r="L1" s="26" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
+      <c r="L1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
@@ -19339,39 +23822,39 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="U2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
       <c r="U3" t="s">
         <v>7</v>
       </c>
@@ -19410,14 +23893,14 @@
       <c r="J4" s="13">
         <v>500000</v>
       </c>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
       <c r="U4" t="s">
         <v>8</v>
       </c>
@@ -19909,10 +24392,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="37"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>6</v>
       </c>
@@ -19930,17 +24413,17 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -20258,61 +24741,61 @@
       <c r="L35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="U35" s="28" t="s">
+      <c r="U35" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="V35" s="28"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
     </row>
     <row r="36" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L36" s="27" t="s">
+      <c r="L36" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
       <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
       <c r="AB37" s="3"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="7" t="s">
         <v>6</v>
       </c>
@@ -20325,55 +24808,55 @@
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="8"/>
-      <c r="L38" s="28" t="s">
+      <c r="L38" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="30"/>
       <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="25"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="27"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="30"/>
+      <c r="X39" s="30"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="30"/>
+      <c r="AA39" s="30"/>
       <c r="AB39" s="3"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
@@ -20407,15 +24890,15 @@
       <c r="J40" s="13">
         <v>500000</v>
       </c>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
@@ -20666,10 +25149,10 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="30"/>
+      <c r="B56" s="32"/>
       <c r="C56" s="7" t="s">
         <v>6</v>
       </c>
@@ -20687,17 +25170,17 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="9"/>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
@@ -21212,27 +25695,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
       <c r="L1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
@@ -21248,17 +25731,17 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -21740,10 +26223,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="37"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>6</v>
       </c>
@@ -21759,17 +26242,17 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -22251,10 +26734,10 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="7" t="s">
         <v>6</v>
       </c>
@@ -22270,17 +26753,17 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="27"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
@@ -22762,10 +27245,10 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="30"/>
+      <c r="B56" s="32"/>
       <c r="C56" s="7" t="s">
         <v>6</v>
       </c>
@@ -22781,17 +27264,17 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="9"/>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
@@ -23301,27 +27784,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
       <c r="L1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
@@ -23337,17 +27820,17 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -23861,10 +28344,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="37"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>16</v>
       </c>
@@ -23880,17 +28363,17 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -24394,10 +28877,10 @@
       <c r="T37" s="6"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="7" t="s">
         <v>16</v>
       </c>
@@ -24413,17 +28896,17 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="27"/>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
@@ -24905,10 +29388,10 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="30"/>
+      <c r="B56" s="32"/>
       <c r="C56" s="7" t="s">
         <v>16</v>
       </c>
@@ -24924,17 +29407,17 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="9"/>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
@@ -25445,27 +29928,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
       <c r="L1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="7" t="s">
         <v>18</v>
       </c>
@@ -25481,17 +29964,17 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -26005,10 +30488,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="37"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>18</v>
       </c>
@@ -26024,17 +30507,17 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -26538,10 +31021,10 @@
       <c r="T37" s="6"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="7" t="s">
         <v>18</v>
       </c>
@@ -26557,17 +31040,17 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="27"/>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
@@ -27049,10 +31532,10 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="30"/>
+      <c r="B56" s="32"/>
       <c r="C56" s="7" t="s">
         <v>18</v>
       </c>
@@ -27068,17 +31551,17 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="9"/>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
@@ -27578,128 +32061,2293 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5307C3D9-74F6-452A-AC30-C83002002A39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475FA8F7-F0D8-41A9-A1D8-FF821E5F615C}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="21" t="s">
+    <row r="1" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
+      <c r="L1" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>109</v>
+      </c>
+      <c r="F5">
+        <v>376</v>
+      </c>
+      <c r="G5">
+        <v>742</v>
+      </c>
+      <c r="H5">
+        <v>3536</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>44</v>
+      </c>
+      <c r="D6">
+        <v>71</v>
+      </c>
+      <c r="E6">
+        <v>103</v>
+      </c>
+      <c r="F6">
+        <v>381</v>
+      </c>
+      <c r="G6">
+        <v>744</v>
+      </c>
+      <c r="H6">
+        <v>3545</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+    </row>
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>67</v>
+      </c>
+      <c r="E7">
+        <v>111</v>
+      </c>
+      <c r="F7">
+        <v>370</v>
+      </c>
+      <c r="G7">
+        <v>746</v>
+      </c>
+      <c r="H7">
+        <v>3524</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+    </row>
+    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>71</v>
+      </c>
+      <c r="E8">
+        <v>104</v>
+      </c>
+      <c r="F8">
+        <v>375</v>
+      </c>
+      <c r="G8">
+        <v>748</v>
+      </c>
+      <c r="H8">
+        <v>3534</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>67</v>
+      </c>
+      <c r="E9">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>382</v>
+      </c>
+      <c r="G9">
+        <v>717</v>
+      </c>
+      <c r="H9">
+        <v>3525</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10">
+        <v>102</v>
+      </c>
+      <c r="F10">
+        <v>385</v>
+      </c>
+      <c r="G10">
+        <v>719</v>
+      </c>
+      <c r="H10">
+        <v>3551</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>36</v>
+      </c>
+      <c r="D11">
+        <v>69</v>
+      </c>
+      <c r="E11">
+        <v>116</v>
+      </c>
+      <c r="F11">
+        <v>372</v>
+      </c>
+      <c r="G11">
+        <v>732</v>
+      </c>
+      <c r="H11">
+        <v>3533</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>32</v>
+      </c>
+      <c r="D12">
+        <v>67</v>
+      </c>
+      <c r="E12">
+        <v>121</v>
+      </c>
+      <c r="F12">
+        <v>383</v>
+      </c>
+      <c r="G12">
+        <v>717</v>
+      </c>
+      <c r="H12">
+        <v>3587</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <v>65</v>
+      </c>
+      <c r="E13">
+        <v>128</v>
+      </c>
+      <c r="F13">
+        <v>394</v>
+      </c>
+      <c r="G13">
+        <v>716</v>
+      </c>
+      <c r="H13">
+        <v>3523</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>68</v>
+      </c>
+      <c r="E14">
+        <v>106</v>
+      </c>
+      <c r="F14">
+        <v>373</v>
+      </c>
+      <c r="G14">
+        <v>721</v>
+      </c>
+      <c r="H14">
+        <v>3544</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1">
+        <f>AVERAGE(B5:B14)</f>
+        <v>25.7</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" ref="C15:J15" si="0">AVERAGE(C5:C14)</f>
+        <v>36</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>68.599999999999994</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>110.8</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>379.1</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>730.2</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="0"/>
+        <v>3540.2</v>
+      </c>
+      <c r="I15" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J15" s="13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <f>_xlfn.STDEV.P(B5:B14)</f>
+        <v>1.7349351572897471</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:I16" si="1">_xlfn.STDEV.P(C5:C14)</f>
+        <v>3.9242833740697169</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>2.0099751242241779</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>8.0349237706402654</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>6.9346953790343235</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>12.882546332150332</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>18.004443895883039</v>
+      </c>
+      <c r="I16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J16" s="15" t="e">
+        <f>_xlfn.STDEV.P(J5:J14)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16">
+        <f>AVERAGE(B16:H16)</f>
+        <v>7.6465432904702295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="19">
+        <f>_xlfn.STDEV.S(B5:B14)</f>
+        <v>1.8287822299126937</v>
+      </c>
+      <c r="C17" s="19">
+        <f t="shared" ref="C17:J17" si="2">_xlfn.STDEV.S(C5:C14)</f>
+        <v>4.1365578819969517</v>
+      </c>
+      <c r="D17" s="19">
+        <f t="shared" si="2"/>
+        <v>2.1186998109427604</v>
+      </c>
+      <c r="E17" s="19">
+        <f t="shared" si="2"/>
+        <v>8.4695533136838641</v>
+      </c>
+      <c r="F17" s="19">
+        <f t="shared" si="2"/>
+        <v>7.3098107590643773</v>
+      </c>
+      <c r="G17" s="19">
+        <f t="shared" si="2"/>
+        <v>13.579396157414363</v>
+      </c>
+      <c r="H17" s="19">
+        <f t="shared" si="2"/>
+        <v>18.978350238568627</v>
+      </c>
+      <c r="I17" s="19" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J17" s="20" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="39"/>
+      <c r="C20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>174</v>
+      </c>
+      <c r="C23">
+        <v>183</v>
+      </c>
+      <c r="D23">
+        <v>222</v>
+      </c>
+      <c r="E23">
+        <v>253</v>
+      </c>
+      <c r="F23">
+        <v>463</v>
+      </c>
+      <c r="G23">
+        <v>646</v>
+      </c>
+      <c r="H23">
+        <v>2127</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>180</v>
+      </c>
+      <c r="C24">
+        <v>183</v>
+      </c>
+      <c r="D24">
+        <v>210</v>
+      </c>
+      <c r="E24">
+        <v>257</v>
+      </c>
+      <c r="F24">
+        <v>478</v>
+      </c>
+      <c r="G24">
+        <v>635</v>
+      </c>
+      <c r="H24">
+        <v>2060</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>174</v>
+      </c>
+      <c r="C25">
+        <v>180</v>
+      </c>
+      <c r="D25">
+        <v>221</v>
+      </c>
+      <c r="E25">
+        <v>256</v>
+      </c>
+      <c r="F25">
+        <v>477</v>
+      </c>
+      <c r="G25">
+        <v>669</v>
+      </c>
+      <c r="H25">
+        <v>2221</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>181</v>
+      </c>
+      <c r="C26">
+        <v>182</v>
+      </c>
+      <c r="D26">
+        <v>206</v>
+      </c>
+      <c r="E26">
+        <v>264</v>
+      </c>
+      <c r="F26">
+        <v>467</v>
+      </c>
+      <c r="G26">
+        <v>639</v>
+      </c>
+      <c r="H26">
+        <v>2277</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>5</v>
+      </c>
+      <c r="B27">
+        <v>183</v>
+      </c>
+      <c r="C27">
+        <v>186</v>
+      </c>
+      <c r="D27">
+        <v>217</v>
+      </c>
+      <c r="E27">
+        <v>252</v>
+      </c>
+      <c r="F27">
+        <v>462</v>
+      </c>
+      <c r="G27">
+        <v>633</v>
+      </c>
+      <c r="H27">
+        <v>2157</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>180</v>
+      </c>
+      <c r="C28">
+        <v>180</v>
+      </c>
+      <c r="D28">
+        <v>206</v>
+      </c>
+      <c r="E28">
+        <v>261</v>
+      </c>
+      <c r="F28">
+        <v>470</v>
+      </c>
+      <c r="G28">
+        <v>657</v>
+      </c>
+      <c r="H28">
+        <v>2202</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>179</v>
+      </c>
+      <c r="C29">
+        <v>178</v>
+      </c>
+      <c r="D29">
+        <v>204</v>
+      </c>
+      <c r="E29">
+        <v>253</v>
+      </c>
+      <c r="F29">
+        <v>479</v>
+      </c>
+      <c r="G29">
+        <v>680</v>
+      </c>
+      <c r="H29">
+        <v>2306</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>8</v>
+      </c>
+      <c r="B30">
+        <v>178</v>
+      </c>
+      <c r="C30">
+        <v>183</v>
+      </c>
+      <c r="D30">
+        <v>213</v>
+      </c>
+      <c r="E30">
+        <v>252</v>
+      </c>
+      <c r="F30">
+        <v>473</v>
+      </c>
+      <c r="G30">
+        <v>610</v>
+      </c>
+      <c r="H30">
+        <v>2092</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>178</v>
+      </c>
+      <c r="C31">
+        <v>179</v>
+      </c>
+      <c r="D31">
+        <v>203</v>
+      </c>
+      <c r="E31">
+        <v>255</v>
+      </c>
+      <c r="F31">
+        <v>486</v>
+      </c>
+      <c r="G31">
+        <v>618</v>
+      </c>
+      <c r="H31">
+        <v>2175</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>10</v>
+      </c>
+      <c r="B32">
+        <v>179</v>
+      </c>
+      <c r="C32">
+        <v>179</v>
+      </c>
+      <c r="D32">
+        <v>210</v>
+      </c>
+      <c r="E32">
+        <v>256</v>
+      </c>
+      <c r="F32">
+        <v>471</v>
+      </c>
+      <c r="G32">
+        <v>630</v>
+      </c>
+      <c r="H32">
+        <v>2308</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" ref="B33:J33" si="3">AVERAGE(B23:B32)</f>
+        <v>178.6</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="3"/>
+        <v>181.3</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="3"/>
+        <v>211.2</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="3"/>
+        <v>255.9</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="3"/>
+        <v>472.6</v>
+      </c>
+      <c r="G33" s="1">
+        <f t="shared" si="3"/>
+        <v>641.70000000000005</v>
+      </c>
+      <c r="H33" s="1">
+        <f t="shared" si="3"/>
+        <v>2192.5</v>
+      </c>
+      <c r="I33" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J33" s="13" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34">
+        <f t="shared" ref="B34:J34" si="4">_xlfn.STDEV.P(B23:B32)</f>
+        <v>2.6907248094147422</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="4"/>
+        <v>2.368543856465402</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="4"/>
+        <v>6.5238025721200366</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="4"/>
+        <v>3.7536648758246911</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="4"/>
+        <v>7.1721684308164431</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="4"/>
+        <v>20.727035485085658</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="4"/>
+        <v>82.327698862533509</v>
+      </c>
+      <c r="I34" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J34" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K34">
+        <f>AVERAGE(B34:H34)</f>
+        <v>17.937662698894353</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="19">
+        <f t="shared" ref="B35:J35" si="5">_xlfn.STDEV.S(B23:B32)</f>
+        <v>2.8362729848243533</v>
+      </c>
+      <c r="C35" s="19">
+        <f t="shared" si="5"/>
+        <v>2.496664441476534</v>
+      </c>
+      <c r="D35" s="19">
+        <f t="shared" si="5"/>
+        <v>6.8766917110547352</v>
+      </c>
+      <c r="E35" s="19">
+        <f t="shared" si="5"/>
+        <v>3.9567101935263782</v>
+      </c>
+      <c r="F35" s="19">
+        <f t="shared" si="5"/>
+        <v>7.5601293345785789</v>
+      </c>
+      <c r="G35" s="19">
+        <f t="shared" si="5"/>
+        <v>21.848213758667882</v>
+      </c>
+      <c r="H35" s="19">
+        <f t="shared" si="5"/>
+        <v>86.781014308686466</v>
+      </c>
+      <c r="I35" s="19" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J35" s="20" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="37"/>
+      <c r="C38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+      <c r="B39" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="27"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="J40" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" s="9">
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <v>350</v>
+      </c>
+      <c r="C41">
+        <v>350</v>
+      </c>
+      <c r="D41">
+        <v>349</v>
+      </c>
+      <c r="E41">
+        <v>352</v>
+      </c>
+      <c r="F41">
+        <v>708</v>
+      </c>
+      <c r="G41">
+        <v>1184</v>
+      </c>
+      <c r="H41">
+        <v>4836</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" s="9">
+        <v>2</v>
+      </c>
+      <c r="B42">
+        <v>345</v>
+      </c>
+      <c r="C42">
+        <v>353</v>
+      </c>
+      <c r="D42">
+        <v>351</v>
+      </c>
+      <c r="E42">
+        <v>355</v>
+      </c>
+      <c r="F42">
+        <v>706</v>
+      </c>
+      <c r="G42">
+        <v>1205</v>
+      </c>
+      <c r="H42">
+        <v>4980</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" s="9">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>350</v>
+      </c>
+      <c r="C43">
+        <v>355</v>
+      </c>
+      <c r="D43">
+        <v>350</v>
+      </c>
+      <c r="E43">
+        <v>352</v>
+      </c>
+      <c r="F43">
+        <v>683</v>
+      </c>
+      <c r="G43">
+        <v>1214</v>
+      </c>
+      <c r="H43">
+        <v>4985</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="9">
+        <v>4</v>
+      </c>
+      <c r="B44">
+        <v>354</v>
+      </c>
+      <c r="C44">
+        <v>349</v>
+      </c>
+      <c r="D44">
+        <v>356</v>
+      </c>
+      <c r="E44">
+        <v>353</v>
+      </c>
+      <c r="F44">
+        <v>723</v>
+      </c>
+      <c r="G44">
+        <v>1171</v>
+      </c>
+      <c r="H44">
+        <v>4880</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>5</v>
+      </c>
+      <c r="B45">
+        <v>347</v>
+      </c>
+      <c r="C45">
+        <v>352</v>
+      </c>
+      <c r="D45">
+        <v>352</v>
+      </c>
+      <c r="E45">
+        <v>356</v>
+      </c>
+      <c r="F45">
+        <v>693</v>
+      </c>
+      <c r="G45">
+        <v>1177</v>
+      </c>
+      <c r="H45">
+        <v>5089</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>6</v>
+      </c>
+      <c r="B46">
+        <v>345</v>
+      </c>
+      <c r="C46">
+        <v>348</v>
+      </c>
+      <c r="D46">
+        <v>350</v>
+      </c>
+      <c r="E46">
+        <v>350</v>
+      </c>
+      <c r="F46">
+        <v>724</v>
+      </c>
+      <c r="G46">
+        <v>1194</v>
+      </c>
+      <c r="H46">
+        <v>4858</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
+        <v>7</v>
+      </c>
+      <c r="B47">
+        <v>352</v>
+      </c>
+      <c r="C47">
+        <v>352</v>
+      </c>
+      <c r="D47">
+        <v>350</v>
+      </c>
+      <c r="E47">
+        <v>358</v>
+      </c>
+      <c r="F47">
+        <v>700</v>
+      </c>
+      <c r="G47">
+        <v>1213</v>
+      </c>
+      <c r="H47">
+        <v>4936</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
+        <v>8</v>
+      </c>
+      <c r="B48">
+        <v>358</v>
+      </c>
+      <c r="C48">
+        <v>350</v>
+      </c>
+      <c r="D48">
+        <v>351</v>
+      </c>
+      <c r="E48">
+        <v>355</v>
+      </c>
+      <c r="F48">
+        <v>703</v>
+      </c>
+      <c r="G48">
+        <v>1222</v>
+      </c>
+      <c r="H48">
+        <v>4820</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="9">
+        <v>9</v>
+      </c>
+      <c r="B49">
+        <v>348</v>
+      </c>
+      <c r="C49">
+        <v>356</v>
+      </c>
+      <c r="D49">
+        <v>349</v>
+      </c>
+      <c r="E49">
+        <v>358</v>
+      </c>
+      <c r="F49">
+        <v>717</v>
+      </c>
+      <c r="G49">
+        <v>1183</v>
+      </c>
+      <c r="H49">
+        <v>4815</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="9">
+        <v>10</v>
+      </c>
+      <c r="B50">
+        <v>358</v>
+      </c>
+      <c r="C50">
+        <v>353</v>
+      </c>
+      <c r="D50">
+        <v>354</v>
+      </c>
+      <c r="E50">
+        <v>357</v>
+      </c>
+      <c r="F50">
+        <v>705</v>
+      </c>
+      <c r="G50">
+        <v>1203</v>
+      </c>
+      <c r="H50">
+        <v>4909</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="1">
+        <f>AVERAGE(B41:B50)</f>
+        <v>350.7</v>
+      </c>
+      <c r="C51" s="1">
+        <f t="shared" ref="C51:J51" si="6">AVERAGE(C41:C50)</f>
+        <v>351.8</v>
+      </c>
+      <c r="D51" s="1">
+        <f t="shared" si="6"/>
+        <v>351.2</v>
+      </c>
+      <c r="E51" s="1">
+        <f t="shared" si="6"/>
+        <v>354.6</v>
+      </c>
+      <c r="F51" s="1">
+        <f t="shared" si="6"/>
+        <v>706.2</v>
+      </c>
+      <c r="G51" s="1">
+        <f t="shared" si="6"/>
+        <v>1196.5999999999999</v>
+      </c>
+      <c r="H51" s="1">
+        <f t="shared" si="6"/>
+        <v>4910.8</v>
+      </c>
+      <c r="I51" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J51" s="13" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <f>_xlfn.STDEV.P(B41:B50)</f>
+        <v>4.5398237851264662</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:J52" si="7">_xlfn.STDEV.P(C41:C50)</f>
+        <v>2.4413111231467406</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="7"/>
+        <v>2.1354156504062622</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="7"/>
+        <v>2.6153393661244042</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="7"/>
+        <v>12.17209924376235</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="7"/>
+        <v>16.487571076419957</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="7"/>
+        <v>83.331626649190042</v>
+      </c>
+      <c r="I52" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J52" s="15" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K52">
+        <f>AVERAGE(B52:H52)</f>
+        <v>17.674740984882316</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="19">
+        <f>_xlfn.STDEV.S(B41:B50)</f>
+        <v>4.7853944456021589</v>
+      </c>
+      <c r="C53" s="19">
+        <f t="shared" ref="C53:J53" si="8">_xlfn.STDEV.S(C41:C50)</f>
+        <v>2.5733678754158378</v>
+      </c>
+      <c r="D53" s="19">
+        <f t="shared" si="8"/>
+        <v>2.2509257354845511</v>
+      </c>
+      <c r="E53" s="19">
+        <f t="shared" si="8"/>
+        <v>2.7568097504180447</v>
+      </c>
+      <c r="F53" s="19">
+        <f t="shared" si="8"/>
+        <v>12.830519171967367</v>
+      </c>
+      <c r="G53" s="19">
+        <f t="shared" si="8"/>
+        <v>17.379425895133718</v>
+      </c>
+      <c r="H53" s="19">
+        <f t="shared" si="8"/>
+        <v>87.839247112741887</v>
+      </c>
+      <c r="I53" s="19" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J53" s="20" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B56" s="32"/>
+      <c r="C56" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+      <c r="B57" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H58" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I58" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="J58" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="9">
+        <v>1</v>
+      </c>
+      <c r="B59">
+        <v>44</v>
+      </c>
+      <c r="C59">
+        <v>44</v>
+      </c>
+      <c r="D59">
+        <v>74</v>
+      </c>
+      <c r="E59">
+        <v>106</v>
+      </c>
+      <c r="F59">
+        <v>282</v>
+      </c>
+      <c r="G59">
+        <v>504</v>
+      </c>
+      <c r="H59">
+        <v>2137</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="9">
+        <v>2</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
+      </c>
+      <c r="C60">
+        <v>46</v>
+      </c>
+      <c r="D60">
+        <v>75</v>
+      </c>
+      <c r="E60">
+        <v>106</v>
+      </c>
+      <c r="F60">
+        <v>283</v>
+      </c>
+      <c r="G60">
+        <v>490</v>
+      </c>
+      <c r="H60">
+        <v>2088</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="9">
+        <v>3</v>
+      </c>
+      <c r="B61">
+        <v>38</v>
+      </c>
+      <c r="C61">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="D61">
+        <v>75</v>
+      </c>
+      <c r="E61">
+        <v>105</v>
+      </c>
+      <c r="F61">
+        <v>288</v>
+      </c>
+      <c r="G61">
+        <v>498</v>
+      </c>
+      <c r="H61">
+        <v>2131</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="9">
+        <v>4</v>
+      </c>
+      <c r="B62">
+        <v>45</v>
+      </c>
+      <c r="C62">
+        <v>45</v>
+      </c>
+      <c r="D62">
+        <v>79</v>
+      </c>
+      <c r="E62">
+        <v>99</v>
+      </c>
+      <c r="F62">
+        <v>287</v>
+      </c>
+      <c r="G62">
+        <v>496</v>
+      </c>
+      <c r="H62">
+        <v>2084</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="9">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>37</v>
+      </c>
+      <c r="C63">
+        <v>46</v>
+      </c>
+      <c r="D63">
+        <v>75</v>
+      </c>
+      <c r="E63">
+        <v>106</v>
+      </c>
+      <c r="F63">
+        <v>289</v>
+      </c>
+      <c r="G63">
+        <v>491</v>
+      </c>
+      <c r="H63">
+        <v>2173</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="9">
         <v>6</v>
       </c>
-      <c r="B3">
-        <f>Points_3070PC!K16</f>
-        <v>24.422247393084064</v>
-      </c>
-      <c r="C3">
-        <f>Points_3070PC!K34</f>
-        <v>23.787775777148777</v>
-      </c>
-      <c r="D3">
-        <f>Points_3070PC!K52</f>
-        <v>25.855458755594153</v>
-      </c>
-      <c r="E3">
-        <f>Points_3070PC!K70</f>
-        <v>9.8523371646058777</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <f>Lines_3070PC!K16</f>
-        <v>6.5957970948918652</v>
-      </c>
-      <c r="C4">
-        <f>Lines_3070PC!K34</f>
-        <v>17.303679147774794</v>
-      </c>
-      <c r="D4">
-        <f>Lines_3070PC!K52</f>
-        <v>15.431984596642508</v>
-      </c>
-      <c r="E4">
-        <f>Lines_3070PC!K70</f>
-        <v>4.8091891328372061</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
-        <f>Polygons_3070PC!K16</f>
-        <v>7.237770871298232</v>
-      </c>
-      <c r="C5">
-        <f>Polygons_3070PC!K34</f>
-        <v>10.085152984072007</v>
-      </c>
-      <c r="D5">
-        <f>Polygons_3070PC!K52</f>
-        <v>8.7128487919588533</v>
-      </c>
-      <c r="E5">
-        <f>Polygons_3070PC!K70</f>
-        <v>4.387905283373482</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="21">
-        <f>AVERAGE(B3:B5)</f>
-        <v>12.751938453091386</v>
-      </c>
-      <c r="C6" s="21">
-        <f>AVERAGE(C3:C5)</f>
-        <v>17.058869302998527</v>
-      </c>
-      <c r="D6" s="21">
-        <f>AVERAGE(D3:D5)</f>
-        <v>16.666764048065172</v>
-      </c>
-      <c r="E6" s="21">
-        <f>AVERAGE(E3:E5)</f>
-        <v>6.3498105269388558</v>
-      </c>
-    </row>
-    <row r="19" spans="8:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="H19" s="23" t="s">
-        <v>54</v>
+      <c r="B64">
+        <v>38</v>
+      </c>
+      <c r="C64">
+        <v>49</v>
+      </c>
+      <c r="D64">
+        <v>77</v>
+      </c>
+      <c r="E64">
+        <v>104</v>
+      </c>
+      <c r="F64">
+        <v>292</v>
+      </c>
+      <c r="G64">
+        <v>499</v>
+      </c>
+      <c r="H64">
+        <v>2147</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="9">
+        <v>7</v>
+      </c>
+      <c r="B65">
+        <v>44</v>
+      </c>
+      <c r="C65">
+        <v>45</v>
+      </c>
+      <c r="D65">
+        <v>75</v>
+      </c>
+      <c r="E65">
+        <v>100</v>
+      </c>
+      <c r="F65">
+        <v>280</v>
+      </c>
+      <c r="G65">
+        <v>487</v>
+      </c>
+      <c r="H65">
+        <v>2097</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="9">
+        <v>8</v>
+      </c>
+      <c r="B66">
+        <v>45</v>
+      </c>
+      <c r="C66">
+        <v>44</v>
+      </c>
+      <c r="D66">
+        <v>72</v>
+      </c>
+      <c r="E66">
+        <v>98</v>
+      </c>
+      <c r="F66">
+        <v>280</v>
+      </c>
+      <c r="G66">
+        <v>482</v>
+      </c>
+      <c r="H66">
+        <v>2082</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="9">
+        <v>9</v>
+      </c>
+      <c r="B67">
+        <v>43</v>
+      </c>
+      <c r="C67">
+        <v>43</v>
+      </c>
+      <c r="D67">
+        <v>77</v>
+      </c>
+      <c r="E67">
+        <v>101</v>
+      </c>
+      <c r="F67">
+        <v>276</v>
+      </c>
+      <c r="G67">
+        <v>512</v>
+      </c>
+      <c r="H67">
+        <v>2106</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="9">
+        <v>10</v>
+      </c>
+      <c r="B68">
+        <v>42</v>
+      </c>
+      <c r="C68">
+        <v>46</v>
+      </c>
+      <c r="D68">
+        <v>81</v>
+      </c>
+      <c r="E68">
+        <v>102</v>
+      </c>
+      <c r="F68">
+        <v>280</v>
+      </c>
+      <c r="G68">
+        <v>498</v>
+      </c>
+      <c r="H68">
+        <v>2083</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="1">
+        <f>AVERAGE(B59:B68)</f>
+        <v>41.4</v>
+      </c>
+      <c r="C69" s="1">
+        <f t="shared" ref="C69:J69" si="9">AVERAGE(C59:C68)</f>
+        <v>45.7</v>
+      </c>
+      <c r="D69" s="1">
+        <f>AVERAGE(D59:D68)</f>
+        <v>76</v>
+      </c>
+      <c r="E69" s="1">
+        <f>AVERAGE(E59:E68)</f>
+        <v>102.7</v>
+      </c>
+      <c r="F69" s="1">
+        <f t="shared" si="9"/>
+        <v>283.7</v>
+      </c>
+      <c r="G69" s="1">
+        <f t="shared" si="9"/>
+        <v>495.7</v>
+      </c>
+      <c r="H69" s="1">
+        <f t="shared" si="9"/>
+        <v>2112.8000000000002</v>
+      </c>
+      <c r="I69" s="1" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J69" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70">
+        <f>_xlfn.STDEV.P(B59:B68)</f>
+        <v>3.1048349392520045</v>
+      </c>
+      <c r="C70">
+        <f t="shared" ref="C70:J70" si="10">_xlfn.STDEV.P(C59:C68)</f>
+        <v>1.9</v>
+      </c>
+      <c r="D70">
+        <f>_xlfn.STDEV.P(D59:D68)</f>
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="E70">
+        <f>_xlfn.STDEV.P(E59:E68)</f>
+        <v>2.9342801502242422</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="10"/>
+        <v>4.7968739820845823</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="10"/>
+        <v>8.2103593100424046</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="10"/>
+        <v>30.47556398165586</v>
+      </c>
+      <c r="I70" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J70" s="15" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K70">
+        <f>AVERAGE(B70:H70)</f>
+        <v>7.6959145865774667</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="19">
+        <f>_xlfn.STDEV.S(B59:B68)</f>
+        <v>3.2727833889689539</v>
+      </c>
+      <c r="C71" s="19">
+        <f t="shared" ref="C71:J71" si="11">_xlfn.STDEV.S(C59:C68)</f>
+        <v>2.0027758514399734</v>
+      </c>
+      <c r="D71" s="19">
+        <f>_xlfn.STDEV.S(D59:D68)</f>
+        <v>2.5819888974716112</v>
+      </c>
+      <c r="E71" s="19">
+        <f>_xlfn.STDEV.S(E59:E68)</f>
+        <v>3.0930028559098792</v>
+      </c>
+      <c r="F71" s="19">
+        <f t="shared" si="11"/>
+        <v>5.0563491440630033</v>
+      </c>
+      <c r="G71" s="19">
+        <f t="shared" si="11"/>
+        <v>8.6544786093675228</v>
+      </c>
+      <c r="H71" s="19">
+        <f t="shared" si="11"/>
+        <v>32.12406505340747</v>
+      </c>
+      <c r="I71" s="19" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J71" s="20" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="A38:B38"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5307C3D9-74F6-452A-AC30-C83002002A39}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <f>Points_3070PC!K16</f>
+        <v>24.422247393084064</v>
+      </c>
+      <c r="C3">
+        <f>Points_3070PC!K34</f>
+        <v>23.787775777148777</v>
+      </c>
+      <c r="D3">
+        <f>Points_3070PC!K52</f>
+        <v>25.855458755594153</v>
+      </c>
+      <c r="E3">
+        <f>Points_3070PC!K70</f>
+        <v>9.8523371646058777</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <f>Lines_3070PC!K16</f>
+        <v>6.5957970948918652</v>
+      </c>
+      <c r="C4">
+        <f>Lines_3070PC!K34</f>
+        <v>17.303679147774794</v>
+      </c>
+      <c r="D4">
+        <f>Lines_3070PC!K52</f>
+        <v>15.431984596642508</v>
+      </c>
+      <c r="E4">
+        <f>Lines_3070PC!K70</f>
+        <v>4.8091891328372061</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <f>Polygons_3070PC!K16</f>
+        <v>7.237770871298232</v>
+      </c>
+      <c r="C5">
+        <f>Polygons_3070PC!K34</f>
+        <v>10.085152984072007</v>
+      </c>
+      <c r="D5">
+        <f>Polygons_3070PC!K52</f>
+        <v>8.7128487919588533</v>
+      </c>
+      <c r="E5">
+        <f>Polygons_3070PC!K70</f>
+        <v>4.387905283373482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6">
+        <f>Combined_3070PC!K16</f>
+        <v>7.6465432904702295</v>
+      </c>
+      <c r="C6">
+        <f>Combined_3070PC!K34</f>
+        <v>17.937662698894353</v>
+      </c>
+      <c r="D6">
+        <f>Combined_3070PC!K52</f>
+        <v>17.674740984882316</v>
+      </c>
+      <c r="E6">
+        <f>Combined_3070PC!K70</f>
+        <v>7.6959145865774667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="21">
+        <f>AVERAGE(B3:B5)</f>
+        <v>12.751938453091386</v>
+      </c>
+      <c r="C7" s="21">
+        <f>AVERAGE(C3:C5)</f>
+        <v>17.058869302998527</v>
+      </c>
+      <c r="D7" s="21">
+        <f>AVERAGE(D3:D5)</f>
+        <v>16.666764048065172</v>
+      </c>
+      <c r="E7" s="21">
+        <f>AVERAGE(E3:E5)</f>
+        <v>6.3498105269388558</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="H20" s="22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1083D35-1455-4A6A-8D2F-88B4EAE334E1}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -27724,23 +34372,23 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
+      <c r="A3" s="42"/>
       <c r="B3" s="1">
         <v>50</v>
       </c>
